--- a/data/trans_orig/IP07C01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C01-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20374</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>33327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47958</t>
+          <t>47445</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58750</t>
+          <t>59106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77181</t>
+          <t>77048</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>35246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31885</t>
+          <t>32284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45389</t>
+          <t>45864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63599</t>
+          <t>63182</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4421</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>628</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65306</t>
+          <t>64453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44417</t>
+          <t>45040</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60224</t>
+          <t>60001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99449</t>
+          <t>99490</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120640</t>
+          <t>121100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28358</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42812</t>
+          <t>43703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27815</t>
+          <t>28412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43003</t>
+          <t>42709</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60891</t>
+          <t>59771</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81759</t>
+          <t>80462</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9802</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26610</t>
+          <t>26663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37925</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36329</t>
+          <t>36686</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54264</t>
+          <t>54028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71053</t>
+          <t>71068</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,98%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15574</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26794</t>
+          <t>26886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>21785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34522</t>
+          <t>34664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40885</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57428</t>
+          <t>58768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>4534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>639</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4486</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>30321</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45193</t>
+          <t>46127</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33787</t>
+          <t>33481</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48053</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69367</t>
+          <t>68454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90156</t>
+          <t>88549</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26058</t>
+          <t>25689</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>40832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49542</t>
+          <t>49895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>64691</t>
+          <t>65317</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>86035</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3644</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>12044</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6799</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5776</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>570</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>141559</t>
+          <t>141139</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>168342</t>
+          <t>168791</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>151488</t>
+          <t>149338</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>179533</t>
+          <t>178687</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>299468</t>
+          <t>299389</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>337717</t>
+          <t>337005</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105827</t>
+          <t>105877</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>133162</t>
+          <t>132311</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>117059</t>
+          <t>117657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>145176</t>
+          <t>145744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>231239</t>
+          <t>231946</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>269357</t>
+          <t>270952</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,13%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>16044</t>
+          <t>15230</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>33339</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>627</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>11059</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2012 (tasa de respuesta: 95,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>26242</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24373</t>
+          <t>24846</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>38392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41925</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61097</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30695</t>
+          <t>29558</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43709</t>
+          <t>42965</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31303</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>44868</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65381</t>
+          <t>66153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85327</t>
+          <t>85589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,88%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2963</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>5898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31526</t>
+          <t>30458</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46948</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36253</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>51081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71111</t>
+          <t>71143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92817</t>
+          <t>92430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>46436</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61783</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38690</t>
+          <t>38734</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54312</t>
+          <t>53832</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89317</t>
+          <t>89804</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111803</t>
+          <t>111859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4419</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32930</t>
+          <t>33004</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>40182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51276</t>
+          <t>50819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69185</t>
+          <t>69276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,86%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>27371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39839</t>
+          <t>40539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23935</t>
+          <t>23785</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36692</t>
+          <t>36554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55212</t>
+          <t>54771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>73902</t>
+          <t>73000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>657</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>439</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6055,7 +6055,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>629</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1489</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37265</t>
+          <t>36647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>29667</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44881</t>
+          <t>45641</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55144</t>
+          <t>55000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76707</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,94%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>40147</t>
+          <t>40221</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56505</t>
+          <t>56170</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>33636</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50032</t>
+          <t>49344</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79979</t>
+          <t>79561</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102331</t>
+          <t>101739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8243</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21348</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7814</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8105</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100129</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126920</t>
+          <t>127878</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>132059</t>
+          <t>130598</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161455</t>
+          <t>160436</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>241060</t>
+          <t>238525</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>282589</t>
+          <t>282153</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>158798</t>
+          <t>157383</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>187618</t>
+          <t>185398</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>142485</t>
+          <t>143224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>171804</t>
+          <t>172721</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>308749</t>
+          <t>309644</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>351898</t>
+          <t>352533</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12092</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>25980</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>22069</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24152</t>
+          <t>23902</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44609</t>
+          <t>42202</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3514</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>18687</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5493</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25555</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39928</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31637</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>46305</t>
+          <t>46461</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62249</t>
+          <t>62920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82702</t>
+          <t>82287</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25313</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39109</t>
+          <t>38707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20063</t>
+          <t>20131</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>49419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69566</t>
+          <t>69627</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>7957</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49494</t>
+          <t>49003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66134</t>
+          <t>65321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44659</t>
+          <t>44521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61723</t>
+          <t>61786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98455</t>
+          <t>98247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>121855</t>
+          <t>121405</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,68%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31807</t>
+          <t>32474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47497</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49558</t>
+          <t>49020</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70658</t>
+          <t>70663</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92433</t>
+          <t>92501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>17156</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -9043,7 +9043,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6642</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37939</t>
+          <t>37652</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50973</t>
+          <t>50671</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53904</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82883</t>
+          <t>82937</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102307</t>
+          <t>101066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>69,93%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16104</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>28821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>14084</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33458</t>
+          <t>35044</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52431</t>
+          <t>52036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9810,7 +9810,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9873,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41362</t>
+          <t>40418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>58917</t>
+          <t>57820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>41578</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58120</t>
+          <t>58322</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,4%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>86844</t>
+          <t>88311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111305</t>
+          <t>112413</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36119</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53563</t>
+          <t>54153</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>37278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>53638</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>78616</t>
+          <t>78168</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>103252</t>
+          <t>101908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>2194</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>9493</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>19966</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -10407,7 +10407,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3355</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170396</t>
+          <t>167309</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>200458</t>
+          <t>199040</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>172603</t>
+          <t>173689</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>205633</t>
+          <t>204028</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>351422</t>
+          <t>354215</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>396568</t>
+          <t>396015</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124635</t>
+          <t>124693</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>154979</t>
+          <t>155355</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>119523</t>
+          <t>120053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>150206</t>
+          <t>150078</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>252660</t>
+          <t>252944</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296672</t>
+          <t>293922</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>12059</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11923</t>
+          <t>12475</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25945</t>
+          <t>27389</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28212</t>
+          <t>28142</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>49743</t>
+          <t>48056</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11089,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de sentirse bien y en forma en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11414</t>
+          <t>11760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19123</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33685</t>
+          <t>34675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57448</t>
+          <t>56118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>26018</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19197</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>40284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3943</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>464</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>26536</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37816</t>
+          <t>38010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40849</t>
+          <t>40697</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62160</t>
+          <t>61133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69954</t>
+          <t>71114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>94839</t>
+          <t>96292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,56%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>28911</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>48290</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>44469</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>67722</t>
+          <t>67419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14198</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5739</t>
+          <t>5807</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3126</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13363</t>
+          <t>13508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13230</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40901</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66748</t>
+          <t>65882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>31209</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50226</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79178</t>
+          <t>79268</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115765</t>
+          <t>116272</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32493</t>
+          <t>32985</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>54796</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13269,7 +13269,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>390</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6366</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5039</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13437,7 +13437,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13452,7 +13452,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29246</t>
+          <t>29104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>20967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34781</t>
+          <t>34939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>41736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59417</t>
+          <t>59345</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30814</t>
+          <t>30668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17069</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30514</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38085</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56389</t>
+          <t>56375</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10775</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16896</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14134,7 +14134,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110456</t>
+          <t>108750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>158813</t>
+          <t>157478</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>129736</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>168026</t>
+          <t>167731</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>248842</t>
+          <t>248949</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>311926</t>
+          <t>316372</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43558</t>
+          <t>44874</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85034</t>
+          <t>85644</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>84104</t>
+          <t>84114</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118807</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14555,7 +14555,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>141756</t>
+          <t>136815</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>196475</t>
+          <t>196646</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,67%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5174</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>16764</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8440</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22131</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>34203</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16559</t>
+          <t>15997</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -14844,7 +14844,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14859,7 +14859,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14929,7 +14929,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
